--- a/Excel para Finanzas - parte 2/Evaluación/Plantilla_Supervisado_Trabajo.xlsx
+++ b/Excel para Finanzas - parte 2/Evaluación/Plantilla_Supervisado_Trabajo.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,18 +505,6 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -529,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,18 +589,6 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -987,11 +963,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIFS(3_Train_NN!$D$10:$D$17, 1, 3_Train_NN!$G$10:$G$17, "&gt;="&amp;$C$2)</f>
+        <f>COUNTIFS('3_Train_NN'!$D$10:$D$17, 1, '3_Train_NN'!$G$10:$G$17, "&gt;="&amp;$C$2)</f>
         <v/>
       </c>
       <c r="D6">
-        <f>COUNTIFS(3_Train_NN!$D$10:$D$17, 1, 3_Train_NN!$G$10:$G$17, "&lt;"&amp;$C$2)</f>
+        <f>COUNTIFS('3_Train_NN'!$D$10:$D$17, 1, '3_Train_NN'!$G$10:$G$17, "&lt;"&amp;$C$2)</f>
         <v/>
       </c>
     </row>
@@ -1002,11 +978,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIFS(3_Train_NN!$D$10:$D$17, 0, 3_Train_NN!$G$10:$G$17, "&gt;="&amp;$C$2)</f>
+        <f>COUNTIFS('3_Train_NN'!$D$10:$D$17, 0, '3_Train_NN'!$G$10:$G$17, "&gt;="&amp;$C$2)</f>
         <v/>
       </c>
       <c r="D7">
-        <f>COUNTIFS(3_Train_NN!$D$10:$D$17, 0, 3_Train_NN!$G$10:$G$17, "&lt;"&amp;$C$2)</f>
+        <f>COUNTIFS('3_Train_NN'!$D$10:$D$17, 0, '3_Train_NN'!$G$10:$G$17, "&lt;"&amp;$C$2)</f>
         <v/>
       </c>
     </row>
